--- a/data/trans_orig/P45C_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P45C_R2-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2007</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97859</t>
+          <t>99891</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>135989</t>
+          <t>137946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107620</t>
+          <t>108401</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>144266</t>
+          <t>146632</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>216291</t>
+          <t>218788</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>270502</t>
+          <t>273052</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>356380</t>
+          <t>354423</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>394510</t>
+          <t>392478</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>321423</t>
+          <t>319057</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>358069</t>
+          <t>357288</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>687556</t>
+          <t>685006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>741767</t>
+          <t>739270</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,42%</t>
+          <t>77,16%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>133015</t>
+          <t>134722</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>177534</t>
+          <t>179143</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95972</t>
+          <t>97730</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133957</t>
+          <t>136150</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241379</t>
+          <t>241399</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>301123</t>
+          <t>302419</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,18%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>556055</t>
+          <t>554446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>600574</t>
+          <t>598867</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>490386</t>
+          <t>488193</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>528371</t>
+          <t>526613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1056808</t>
+          <t>1055512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1116552</t>
+          <t>1116532</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77945</t>
+          <t>76474</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>112792</t>
+          <t>112771</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62854</t>
+          <t>63341</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95438</t>
+          <t>96697</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148580</t>
+          <t>150369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>197319</t>
+          <t>200824</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,14%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525064</t>
+          <t>525085</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>559911</t>
+          <t>561382</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>593326</t>
+          <t>592067</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>625910</t>
+          <t>625423</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1129301</t>
+          <t>1125796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1178040</t>
+          <t>1176251</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,67%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65854</t>
+          <t>67198</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100164</t>
+          <t>101323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37751</t>
+          <t>38647</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64572</t>
+          <t>64236</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111608</t>
+          <t>112314</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157397</t>
+          <t>155945</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>417834</t>
+          <t>416675</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>452144</t>
+          <t>450800</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449044</t>
+          <t>449380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>475865</t>
+          <t>474969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>874217</t>
+          <t>875669</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>920006</t>
+          <t>919300</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>26596</t>
+          <t>27047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>50198</t>
+          <t>49111</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19339</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40375</t>
+          <t>39209</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52005</t>
+          <t>51740</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81720</t>
+          <t>81586</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>335445</t>
+          <t>336532</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>359047</t>
+          <t>358596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>363611</t>
+          <t>364777</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>384647</t>
+          <t>385964</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>707909</t>
+          <t>708043</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>737624</t>
+          <t>737889</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8542</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>23911</t>
+          <t>24665</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8601</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24501</t>
+          <t>23385</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21394</t>
+          <t>20997</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41567</t>
+          <t>42214</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267616</t>
+          <t>266862</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282985</t>
+          <t>282562</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>318433</t>
+          <t>319549</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>334333</t>
+          <t>334120</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>592894</t>
+          <t>592247</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>613067</t>
+          <t>613464</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,69%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6666</t>
+          <t>6414</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>20113</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1177</t>
+          <t>1225</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11561</t>
+          <t>11419</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>9467</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>28065</t>
+          <t>26273</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>189089</t>
+          <t>189770</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>203217</t>
+          <t>203469</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>320106</t>
+          <t>320248</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>330490</t>
+          <t>330442</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>513485</t>
+          <t>515277</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>531716</t>
+          <t>532083</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>470835</t>
+          <t>471293</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>553488</t>
+          <t>558570</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>380482</t>
+          <t>384174</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>456084</t>
+          <t>457603</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>873613</t>
+          <t>873195</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>990516</t>
+          <t>991115</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2715376</t>
+          <t>2710294</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2798029</t>
+          <t>2797571</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2914915</t>
+          <t>2913396</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2990517</t>
+          <t>2986825</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5649348</t>
+          <t>5648749</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5766251</t>
+          <t>5766669</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2012</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2012 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123037</t>
+          <t>124954</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163128</t>
+          <t>163515</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110521</t>
+          <t>110655</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>147211</t>
+          <t>148435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>246564</t>
+          <t>243902</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>298394</t>
+          <t>297197</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>33,9%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287533</t>
+          <t>287146</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>327624</t>
+          <t>325707</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278817</t>
+          <t>277593</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>315507</t>
+          <t>315373</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>578295</t>
+          <t>579492</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>630125</t>
+          <t>632787</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>72,18%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>146342</t>
+          <t>148534</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>193372</t>
+          <t>193243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72280</t>
+          <t>72104</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107564</t>
+          <t>108126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>227940</t>
+          <t>227828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>285307</t>
+          <t>287609</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>488950</t>
+          <t>489079</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>535980</t>
+          <t>533788</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500763</t>
+          <t>500201</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>536047</t>
+          <t>536223</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1005342</t>
+          <t>1003040</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1062709</t>
+          <t>1062821</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92772</t>
+          <t>93037</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>131529</t>
+          <t>134469</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>87984</t>
+          <t>88791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128327</t>
+          <t>128406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>193391</t>
+          <t>194638</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>247127</t>
+          <t>250914</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,14%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>547492</t>
+          <t>544552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>586249</t>
+          <t>585984</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>576130</t>
+          <t>576051</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>616473</t>
+          <t>615666</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1136351</t>
+          <t>1132564</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1190087</t>
+          <t>1188840</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>81,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>85,93%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>84293</t>
+          <t>83299</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>120793</t>
+          <t>119461</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55784</t>
+          <t>55544</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89050</t>
+          <t>88943</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147553</t>
+          <t>149013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>196700</t>
+          <t>198522</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>487478</t>
+          <t>488810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>523978</t>
+          <t>524972</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>522875</t>
+          <t>522982</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>556141</t>
+          <t>556381</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1023496</t>
+          <t>1021674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1072643</t>
+          <t>1071183</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>31492</t>
+          <t>32428</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>55792</t>
+          <t>57257</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>29896</t>
+          <t>30692</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55266</t>
+          <t>55579</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>66471</t>
+          <t>68541</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>102052</t>
+          <t>103507</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,86%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>371566</t>
+          <t>370101</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>395866</t>
+          <t>394930</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>390394</t>
+          <t>390081</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>415764</t>
+          <t>414968</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>770966</t>
+          <t>769511</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>806547</t>
+          <t>804477</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13885</t>
+          <t>13913</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32108</t>
+          <t>32509</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>30134</t>
+          <t>31661</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31768</t>
+          <t>30671</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56497</t>
+          <t>56033</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,54%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274739</t>
+          <t>274338</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292962</t>
+          <t>292934</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>318907</t>
+          <t>317380</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>336353</t>
+          <t>336490</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>599391</t>
+          <t>599855</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>624120</t>
+          <t>625217</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15138</t>
+          <t>14824</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>10567</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28169</t>
+          <t>27533</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16130</t>
+          <t>16387</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35981</t>
+          <t>36541</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229430</t>
+          <t>229744</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241364</t>
+          <t>241421</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>349821</t>
+          <t>350457</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>368020</t>
+          <t>367423</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>586577</t>
+          <t>586017</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>606428</t>
+          <t>606171</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>553901</t>
+          <t>551193</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>642646</t>
+          <t>641753</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>430882</t>
+          <t>431953</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>516401</t>
+          <t>515392</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1015275</t>
+          <t>1012265</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1135391</t>
+          <t>1136203</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,41%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2756401</t>
+          <t>2757294</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2845146</t>
+          <t>2847854</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3007026</t>
+          <t>3008035</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3092545</t>
+          <t>3091474</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5787084</t>
+          <t>5786272</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5907200</t>
+          <t>5910210</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2016</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83434</t>
+          <t>83140</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>119652</t>
+          <t>118111</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81427</t>
+          <t>80700</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>115527</t>
+          <t>113043</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>175924</t>
+          <t>173868</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223749</t>
+          <t>223396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>295160</t>
+          <t>296701</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>331378</t>
+          <t>331672</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>279202</t>
+          <t>281686</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>313302</t>
+          <t>314029</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,73%</t>
+          <t>71,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>585793</t>
+          <t>586146</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>633618</t>
+          <t>635674</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,52%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>92535</t>
+          <t>90319</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>130068</t>
+          <t>128544</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105500</t>
+          <t>107361</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144031</t>
+          <t>145626</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>210726</t>
+          <t>206207</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>265325</t>
+          <t>259940</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>455212</t>
+          <t>456736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>492745</t>
+          <t>494961</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>418573</t>
+          <t>416978</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>457104</t>
+          <t>455243</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>882559</t>
+          <t>887944</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>937158</t>
+          <t>941677</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65269</t>
+          <t>65178</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>99011</t>
+          <t>98906</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73102</t>
+          <t>71946</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>107079</t>
+          <t>106089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>145672</t>
+          <t>148551</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193273</t>
+          <t>198830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>567082</t>
+          <t>567187</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>600824</t>
+          <t>600915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>549717</t>
+          <t>550707</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>583694</t>
+          <t>584850</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1129616</t>
+          <t>1124059</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1177217</t>
+          <t>1174338</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>88,77%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62018</t>
+          <t>63326</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96392</t>
+          <t>95301</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56422</t>
+          <t>56627</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88223</t>
+          <t>90505</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125896</t>
+          <t>128018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174580</t>
+          <t>174845</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>546484</t>
+          <t>547575</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>580858</t>
+          <t>579550</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>554485</t>
+          <t>552203</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>586286</t>
+          <t>586081</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1111004</t>
+          <t>1110739</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1159688</t>
+          <t>1157566</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36566</t>
+          <t>37850</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>64806</t>
+          <t>65452</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67819</t>
+          <t>67447</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>83278</t>
+          <t>84411</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>121771</t>
+          <t>123108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,72%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>409642</t>
+          <t>408996</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>437882</t>
+          <t>436598</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>425408</t>
+          <t>425780</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>454662</t>
+          <t>454826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>845905</t>
+          <t>844568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>884398</t>
+          <t>883265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,39%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>13545</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32366</t>
+          <t>32781</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8426,7 +8426,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18692</t>
+          <t>19922</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40107</t>
+          <t>41830</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36986</t>
+          <t>36351</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64590</t>
+          <t>64356</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>297114</t>
+          <t>296699</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>315931</t>
+          <t>315935</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,7 +8534,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,18%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>332640</t>
+          <t>330917</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>354055</t>
+          <t>352825</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>637637</t>
+          <t>637871</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>665241</t>
+          <t>665876</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5977</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19107</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7542</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>23918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16592</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37700</t>
+          <t>38752</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233175</t>
+          <t>232468</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>246305</t>
+          <t>245810</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>370555</t>
+          <t>371478</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387854</t>
+          <t>387723</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>609979</t>
+          <t>608927</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>631087</t>
+          <t>630746</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>417035</t>
+          <t>411298</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>500918</t>
+          <t>496714</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,47 +9107,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>14,76%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>463</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>477446</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>436026</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>517030</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>13,57%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>12,39%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>463</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>477446</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>437175</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>516935</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>13,57%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>870594</t>
+          <t>876401</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>993009</t>
+          <t>986589</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2864354</t>
+          <t>2868558</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2948237</t>
+          <t>2953974</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,49 +9220,49 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>87,78%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>3040762</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3001178</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3082182</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>86,43%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>85,3%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>87,61%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2852</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3040762</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3001273</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>3081033</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>86,43%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>85,31%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>5633</t>
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5890471</t>
+          <t>5896891</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6012886</t>
+          <t>6007079</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2023</t>
+          <t>Población que ha sufrido alguna quemadura solar (con o sin ampollas) en el último año en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58283</t>
+          <t>58356</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115671</t>
+          <t>116165</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50454</t>
+          <t>50933</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>88932</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>122158</t>
+          <t>121592</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>188286</t>
+          <t>193876</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284316</t>
+          <t>283822</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>341704</t>
+          <t>341631</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>222928</t>
+          <t>224268</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262746</t>
+          <t>262267</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,18%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>524901</t>
+          <t>519311</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>591029</t>
+          <t>591595</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87949</t>
+          <t>88307</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135158</t>
+          <t>134080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55648</t>
+          <t>52754</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114086</t>
+          <t>112735</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>155137</t>
+          <t>151028</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>235310</t>
+          <t>236521</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,3%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>288389</t>
+          <t>289467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335598</t>
+          <t>335240</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>397256</t>
+          <t>398607</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455694</t>
+          <t>458588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>699579</t>
+          <t>698368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>779752</t>
+          <t>783861</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,85%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92962</t>
+          <t>92023</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>130312</t>
+          <t>132373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71819</t>
+          <t>72598</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99769</t>
+          <t>99797</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172721</t>
+          <t>174138</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>220648</t>
+          <t>220773</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>402271</t>
+          <t>400210</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>439621</t>
+          <t>440560</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,53%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442699</t>
+          <t>442671</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>470649</t>
+          <t>469870</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>854402</t>
+          <t>854277</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>902329</t>
+          <t>900912</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,8%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41872</t>
+          <t>44665</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>144353</t>
+          <t>148151</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78415</t>
+          <t>76124</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110806</t>
+          <t>109573</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>116337</t>
+          <t>110420</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237726</t>
+          <t>237777</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>742306</t>
+          <t>738508</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>844787</t>
+          <t>841994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>600342</t>
+          <t>601575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>632733</t>
+          <t>635024</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1360081</t>
+          <t>1360030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1481470</t>
+          <t>1487387</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10902,7 +10902,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60901</t>
+          <t>60318</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90361</t>
+          <t>90297</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53150</t>
+          <t>52283</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76233</t>
+          <t>75259</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120350</t>
+          <t>121235</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158714</t>
+          <t>158826</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>469867</t>
+          <t>469931</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>499327</t>
+          <t>499910</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>471123</t>
+          <t>472097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>494206</t>
+          <t>495073</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>948870</t>
+          <t>948758</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>987234</t>
+          <t>986349</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,05%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25765</t>
+          <t>25799</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43446</t>
+          <t>44282</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10795</t>
+          <t>9687</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46153</t>
+          <t>46214</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29548</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>81780</t>
+          <t>82508</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>323662</t>
+          <t>322826</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>341343</t>
+          <t>341309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>561622</t>
+          <t>561561</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>596980</t>
+          <t>598088</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>893103</t>
+          <t>892375</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>945335</t>
+          <t>944476</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>15258</t>
+          <t>14821</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29310</t>
+          <t>28038</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>14897</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26376</t>
+          <t>27044</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32968</t>
+          <t>32898</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51139</t>
+          <t>51263</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11818,7 +11818,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>253108</t>
+          <t>254380</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>267160</t>
+          <t>267597</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>399455</t>
+          <t>398787</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>411233</t>
+          <t>410934</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>657110</t>
+          <t>656986</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>675281</t>
+          <t>675351</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,7 +11926,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>427918</t>
+          <t>415959</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>596289</t>
+          <t>602016</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>371769</t>
+          <t>367559</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>501114</t>
+          <t>499047</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>856184</t>
+          <t>850031</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1066815</t>
+          <t>1071214</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2856241</t>
+          <t>2850514</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3024612</t>
+          <t>3036571</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3158006</t>
+          <t>3160073</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3287351</t>
+          <t>3291561</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6044835</t>
+          <t>6040436</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6255466</t>
+          <t>6261619</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P45C_R2-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P45C_R2-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99891</t>
+          <t>99826</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>137946</t>
+          <t>136480</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>108401</t>
+          <t>107349</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146632</t>
+          <t>144138</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>218788</t>
+          <t>218999</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>273052</t>
+          <t>270499</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>354423</t>
+          <t>355889</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392478</t>
+          <t>392543</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319057</t>
+          <t>321551</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>357288</t>
+          <t>358340</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>69,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>685006</t>
+          <t>687559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>739270</t>
+          <t>739059</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,16%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>134722</t>
+          <t>134116</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>179143</t>
+          <t>178780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>97730</t>
+          <t>96824</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136150</t>
+          <t>136419</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>241399</t>
+          <t>240479</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>302419</t>
+          <t>298022</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>554446</t>
+          <t>554809</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>598867</t>
+          <t>599473</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,64%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>488193</t>
+          <t>487924</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>526613</t>
+          <t>527519</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1055512</t>
+          <t>1059909</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1116532</t>
+          <t>1117452</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>76474</t>
+          <t>77169</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>112771</t>
+          <t>112324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63341</t>
+          <t>64941</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96697</t>
+          <t>98075</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150369</t>
+          <t>146859</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>200824</t>
+          <t>197495</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525085</t>
+          <t>525532</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>561382</t>
+          <t>560687</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>592067</t>
+          <t>590689</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>625423</t>
+          <t>623823</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1125796</t>
+          <t>1129125</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1176251</t>
+          <t>1179761</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67198</t>
+          <t>68330</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101323</t>
+          <t>102188</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>38647</t>
+          <t>38731</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64236</t>
+          <t>66177</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112314</t>
+          <t>112104</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155945</t>
+          <t>156358</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>416675</t>
+          <t>415810</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>450800</t>
+          <t>449668</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>449380</t>
+          <t>447439</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>474969</t>
+          <t>474885</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>875669</t>
+          <t>875256</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>919300</t>
+          <t>919510</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,11%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27047</t>
+          <t>26294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49111</t>
+          <t>48458</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>19735</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39209</t>
+          <t>39929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51740</t>
+          <t>50259</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81586</t>
+          <t>81606</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>336532</t>
+          <t>337185</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>358596</t>
+          <t>359349</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>364777</t>
+          <t>364057</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>385964</t>
+          <t>384251</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>708043</t>
+          <t>708023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>737889</t>
+          <t>739370</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,64%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24665</t>
+          <t>25135</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8388</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23385</t>
+          <t>23444</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20997</t>
+          <t>21253</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42214</t>
+          <t>42180</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266862</t>
+          <t>266392</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>282562</t>
+          <t>282493</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>319549</t>
+          <t>319490</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>334120</t>
+          <t>334546</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>592247</t>
+          <t>592281</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>613464</t>
+          <t>613208</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,65%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6414</t>
+          <t>6579</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>20113</t>
+          <t>20491</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,82 +2806,82 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>3,13%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>4589</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1167</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>10510</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>16545</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>25882</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
           <t>3,06%</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>4589</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>11419</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>16545</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>9467</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>26273</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>189770</t>
+          <t>189392</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>203469</t>
+          <t>203304</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,82 +2919,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>96,87%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>327078</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>321157</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>330500</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>99,65%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>525005</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>515668</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>531758</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
           <t>96,94%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>327078</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>320248</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>330442</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>98,62%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>99,63%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>525005</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>515277</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>532083</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>96,94%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>471293</t>
+          <t>472239</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>558570</t>
+          <t>557285</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>384174</t>
+          <t>380718</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>457603</t>
+          <t>459893</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>873195</t>
+          <t>880119</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>991115</t>
+          <t>988972</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2710294</t>
+          <t>2711579</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2797571</t>
+          <t>2796625</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2913396</t>
+          <t>2911106</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2986825</t>
+          <t>2990281</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5648749</t>
+          <t>5650892</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5766669</t>
+          <t>5759745</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124954</t>
+          <t>124864</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163515</t>
+          <t>163082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>110655</t>
+          <t>110131</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148435</t>
+          <t>147710</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>25,97%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>243902</t>
+          <t>241834</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>297197</t>
+          <t>299023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287146</t>
+          <t>287579</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>325707</t>
+          <t>325797</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>277593</t>
+          <t>278318</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>315373</t>
+          <t>315897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,16%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>579492</t>
+          <t>577666</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>632787</t>
+          <t>634855</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,42%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148534</t>
+          <t>145299</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>193243</t>
+          <t>191300</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72104</t>
+          <t>73214</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>108126</t>
+          <t>109644</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>227828</t>
+          <t>231948</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>287609</t>
+          <t>293447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,74%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>489079</t>
+          <t>491022</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>533788</t>
+          <t>537023</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>78,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>500201</t>
+          <t>498683</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>536223</t>
+          <t>535113</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1003040</t>
+          <t>997202</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1062821</t>
+          <t>1058701</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>93037</t>
+          <t>91938</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>134469</t>
+          <t>131961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>88791</t>
+          <t>90193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128406</t>
+          <t>129610</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194638</t>
+          <t>191662</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>250914</t>
+          <t>249665</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,05%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>544552</t>
+          <t>547060</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>585984</t>
+          <t>587083</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>576051</t>
+          <t>574847</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>615666</t>
+          <t>614264</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1132564</t>
+          <t>1133813</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1188840</t>
+          <t>1191816</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>86,15%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83299</t>
+          <t>84651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119461</t>
+          <t>121520</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55544</t>
+          <t>56225</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88943</t>
+          <t>89324</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149013</t>
+          <t>148067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198522</t>
+          <t>198795</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>488810</t>
+          <t>486751</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>524972</t>
+          <t>523620</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>522982</t>
+          <t>522601</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>556381</t>
+          <t>555700</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1021674</t>
+          <t>1021401</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1071183</t>
+          <t>1072129</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,87%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32428</t>
+          <t>31887</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57257</t>
+          <t>56569</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55579</t>
+          <t>55088</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68541</t>
+          <t>68819</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>103507</t>
+          <t>102830</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>370101</t>
+          <t>370789</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>394930</t>
+          <t>395471</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>390081</t>
+          <t>390572</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>769511</t>
+          <t>770188</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>804477</t>
+          <t>804199</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>15311</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32509</t>
+          <t>34011</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t>11740</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>31661</t>
+          <t>30989</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30671</t>
+          <t>31500</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56033</t>
+          <t>58452</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>274338</t>
+          <t>272836</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>292934</t>
+          <t>291536</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>88,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,47%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>317380</t>
+          <t>318052</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>336490</t>
+          <t>337301</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>599855</t>
+          <t>597436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>625217</t>
+          <t>624388</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3147</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14824</t>
+          <t>14865</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>10722</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27533</t>
+          <t>26895</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16387</t>
+          <t>16984</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36541</t>
+          <t>36846</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>229744</t>
+          <t>229703</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>241421</t>
+          <t>241395</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>350457</t>
+          <t>351095</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>367423</t>
+          <t>367268</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>586017</t>
+          <t>585712</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>606171</t>
+          <t>605574</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,27%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>551193</t>
+          <t>551494</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>641753</t>
+          <t>643560</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>431953</t>
+          <t>438102</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>515392</t>
+          <t>517413</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1012265</t>
+          <t>1012196</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1136203</t>
+          <t>1131831</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2757294</t>
+          <t>2755487</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2847854</t>
+          <t>2847553</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3008035</t>
+          <t>3006014</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3091474</t>
+          <t>3085325</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5786272</t>
+          <t>5790644</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5910210</t>
+          <t>5910279</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83140</t>
+          <t>83605</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>118111</t>
+          <t>119033</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80700</t>
+          <t>81011</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113043</t>
+          <t>112837</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>173868</t>
+          <t>171846</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>223396</t>
+          <t>221548</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,37%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>296701</t>
+          <t>295779</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>331672</t>
+          <t>331207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>281686</t>
+          <t>281892</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>314029</t>
+          <t>313718</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,36%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,48%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>586146</t>
+          <t>587994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>635674</t>
+          <t>637696</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,77%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>90319</t>
+          <t>92434</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>128544</t>
+          <t>130590</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>107361</t>
+          <t>107062</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145626</t>
+          <t>145118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>206207</t>
+          <t>208941</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>259940</t>
+          <t>263162</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>456736</t>
+          <t>454690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494961</t>
+          <t>492846</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416978</t>
+          <t>417486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>455243</t>
+          <t>455542</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887944</t>
+          <t>884722</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>941677</t>
+          <t>938943</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65178</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98906</t>
+          <t>100015</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71946</t>
+          <t>70607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106089</t>
+          <t>104557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>148551</t>
+          <t>147821</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198830</t>
+          <t>195627</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>567187</t>
+          <t>566078</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>600915</t>
+          <t>600012</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>550707</t>
+          <t>552239</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>584850</t>
+          <t>586189</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1124059</t>
+          <t>1127262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1174338</t>
+          <t>1175068</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63326</t>
+          <t>61912</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95301</t>
+          <t>96511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>56627</t>
+          <t>57320</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90505</t>
+          <t>90037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>128018</t>
+          <t>130004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174845</t>
+          <t>174968</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,61%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>547575</t>
+          <t>546365</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>579550</t>
+          <t>580964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>552203</t>
+          <t>552671</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>586081</t>
+          <t>585388</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1110739</t>
+          <t>1110616</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1157566</t>
+          <t>1155580</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>37850</t>
+          <t>37325</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>65452</t>
+          <t>65916</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38892</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67447</t>
+          <t>68589</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>84411</t>
+          <t>82879</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>123108</t>
+          <t>123184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>408996</t>
+          <t>408532</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>436598</t>
+          <t>437123</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>425780</t>
+          <t>424638</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>454826</t>
+          <t>454335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>844568</t>
+          <t>844492</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>883265</t>
+          <t>884797</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>91,44%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13545</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>31111</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19922</t>
+          <t>19853</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41830</t>
+          <t>41212</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36351</t>
+          <t>37317</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64356</t>
+          <t>65220</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,29%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>296699</t>
+          <t>298369</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>315935</t>
+          <t>316081</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>330917</t>
+          <t>331535</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>352825</t>
+          <t>352894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>637871</t>
+          <t>637007</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>665876</t>
+          <t>664910</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,69%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23918</t>
+          <t>23396</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8799,12 +8799,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16933</t>
+          <t>16767</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38752</t>
+          <t>37878</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>232468</t>
+          <t>231862</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>245810</t>
+          <t>245841</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>371478</t>
+          <t>372000</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>387723</t>
+          <t>387622</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8912,12 +8912,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>608927</t>
+          <t>609801</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>630746</t>
+          <t>630912</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,41%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>411298</t>
+          <t>411999</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>496714</t>
+          <t>493086</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>436026</t>
+          <t>437319</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>517030</t>
+          <t>520957</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>876401</t>
+          <t>876199</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>986589</t>
+          <t>990913</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2868558</t>
+          <t>2872186</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2953974</t>
+          <t>2953273</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3001178</t>
+          <t>2997251</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3082182</t>
+          <t>3080889</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5896891</t>
+          <t>5892567</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6007079</t>
+          <t>6007281</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,7 +9290,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>83301</t>
+          <t>87907</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>58356</t>
+          <t>61195</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>116165</t>
+          <t>113294</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>68905</t>
+          <t>76576</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50933</t>
+          <t>57308</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>88932</t>
+          <t>99109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>152207</t>
+          <t>164483</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121592</t>
+          <t>131064</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>193876</t>
+          <t>198049</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>25,71%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>316686</t>
+          <t>319886</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>283822</t>
+          <t>294499</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>341631</t>
+          <t>346598</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>72,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>244295</t>
+          <t>285936</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>224268</t>
+          <t>263403</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>262267</t>
+          <t>305204</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>560980</t>
+          <t>605822</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>519311</t>
+          <t>572256</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>591595</t>
+          <t>639241</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>110044</t>
+          <t>127312</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88307</t>
+          <t>103492</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>134080</t>
+          <t>159168</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89988</t>
+          <t>97134</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>52754</t>
+          <t>78599</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112735</t>
+          <t>116511</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>200032</t>
+          <t>224446</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>151028</t>
+          <t>195570</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236521</t>
+          <t>259408</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>313503</t>
+          <t>349578</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>289467</t>
+          <t>317722</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>335240</t>
+          <t>373398</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>421354</t>
+          <t>402511</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>398607</t>
+          <t>383134</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>458588</t>
+          <t>421046</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>734857</t>
+          <t>752089</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>698368</t>
+          <t>717127</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>783861</t>
+          <t>780965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>73,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>79,97%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511342</t>
+          <t>499645</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511342</t>
+          <t>499645</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511342</t>
+          <t>499645</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>934889</t>
+          <t>976535</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>934889</t>
+          <t>976535</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>934889</t>
+          <t>976535</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>111202</t>
+          <t>127946</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>92023</t>
+          <t>106975</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>132373</t>
+          <t>151074</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>85184</t>
+          <t>97380</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72598</t>
+          <t>80159</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99797</t>
+          <t>112786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>196386</t>
+          <t>225326</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>174138</t>
+          <t>198989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>220773</t>
+          <t>253860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,49%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>421381</t>
+          <t>489044</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>400210</t>
+          <t>465916</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>440560</t>
+          <t>510015</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>457284</t>
+          <t>524759</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442671</t>
+          <t>509353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>469870</t>
+          <t>541980</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>878664</t>
+          <t>1013803</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>854277</t>
+          <t>985269</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>900912</t>
+          <t>1040140</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,94%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>532583</t>
+          <t>616990</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>532583</t>
+          <t>616990</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>532583</t>
+          <t>616990</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1075050</t>
+          <t>1239129</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1075050</t>
+          <t>1239129</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1075050</t>
+          <t>1239129</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,32 +10694,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>98490</t>
+          <t>110068</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44665</t>
+          <t>91306</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>148151</t>
+          <t>132313</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10729,32 +10729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>94722</t>
+          <t>102451</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>76124</t>
+          <t>87310</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>109573</t>
+          <t>117611</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>193213</t>
+          <t>212519</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>110420</t>
+          <t>185831</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>237777</t>
+          <t>235615</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>16,43%</t>
         </is>
       </c>
     </row>
@@ -10807,32 +10807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>788169</t>
+          <t>589361</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>738508</t>
+          <t>567116</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>841994</t>
+          <t>608123</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10842,32 +10842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>616426</t>
+          <t>632525</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>601575</t>
+          <t>617365</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>635024</t>
+          <t>647666</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1404594</t>
+          <t>1221886</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1360030</t>
+          <t>1198790</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1487387</t>
+          <t>1248574</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>886659</t>
+          <t>699429</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>886659</t>
+          <t>699429</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>886659</t>
+          <t>699429</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>711148</t>
+          <t>734976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>711148</t>
+          <t>734976</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>711148</t>
+          <t>734976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1597807</t>
+          <t>1434405</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1597807</t>
+          <t>1434405</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1597807</t>
+          <t>1434405</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>74442</t>
+          <t>81012</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>60318</t>
+          <t>64659</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90297</t>
+          <t>96371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>63540</t>
+          <t>71769</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52283</t>
+          <t>59743</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75259</t>
+          <t>83690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>137981</t>
+          <t>152780</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>121235</t>
+          <t>134294</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>158826</t>
+          <t>175210</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>485786</t>
+          <t>527284</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>469931</t>
+          <t>511925</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>499910</t>
+          <t>543637</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>483816</t>
+          <t>536450</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>472097</t>
+          <t>524529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>495073</t>
+          <t>548476</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>969603</t>
+          <t>1063735</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>948758</t>
+          <t>1041305</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>986349</t>
+          <t>1082221</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,96%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>560228</t>
+          <t>608296</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>560228</t>
+          <t>608296</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>560228</t>
+          <t>608296</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>547356</t>
+          <t>608219</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>547356</t>
+          <t>608219</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>547356</t>
+          <t>608219</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1107584</t>
+          <t>1216515</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1107584</t>
+          <t>1216515</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1107584</t>
+          <t>1216515</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>33427</t>
+          <t>40253</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25799</t>
+          <t>31002</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44282</t>
+          <t>51629</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>28042</t>
+          <t>30290</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>23163</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46214</t>
+          <t>38221</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>61469</t>
+          <t>70544</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30407</t>
+          <t>58494</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82508</t>
+          <t>85313</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>333681</t>
+          <t>365761</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>322826</t>
+          <t>354385</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>341309</t>
+          <t>375012</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>579733</t>
+          <t>408268</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>561561</t>
+          <t>400337</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>598088</t>
+          <t>415395</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>913414</t>
+          <t>774027</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>892375</t>
+          <t>759258</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>944476</t>
+          <t>786077</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>93,07%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>367108</t>
+          <t>406014</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>367108</t>
+          <t>406014</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>367108</t>
+          <t>406014</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>607775</t>
+          <t>438558</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>607775</t>
+          <t>438558</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>607775</t>
+          <t>438558</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>974883</t>
+          <t>844571</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>974883</t>
+          <t>844571</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>974883</t>
+          <t>844571</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>21110</t>
+          <t>23701</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14821</t>
+          <t>17424</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>28038</t>
+          <t>32388</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>21789</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14897</t>
+          <t>15835</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>27044</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>45490</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32898</t>
+          <t>35802</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>51263</t>
+          <t>55367</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>261308</t>
+          <t>286154</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>254380</t>
+          <t>277467</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>267597</t>
+          <t>292431</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>405770</t>
+          <t>442820</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>398787</t>
+          <t>434747</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>410934</t>
+          <t>448774</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>667078</t>
+          <t>728974</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>656986</t>
+          <t>719097</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>675351</t>
+          <t>738662</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,38%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282418</t>
+          <t>309855</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282418</t>
+          <t>309855</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282418</t>
+          <t>309855</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708249</t>
+          <t>774464</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708249</t>
+          <t>774464</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708249</t>
+          <t>774464</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>532017</t>
+          <t>598199</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>415959</t>
+          <t>546737</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>602016</t>
+          <t>656550</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>450443</t>
+          <t>497389</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>367559</t>
+          <t>459725</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>499047</t>
+          <t>538703</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>982460</t>
+          <t>1095588</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>850031</t>
+          <t>1034481</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1071214</t>
+          <t>1166270</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2920513</t>
+          <t>2927068</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2850514</t>
+          <t>2868717</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3036571</t>
+          <t>2978530</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3208677</t>
+          <t>3233269</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3160073</t>
+          <t>3191955</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3291561</t>
+          <t>3270933</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6129190</t>
+          <t>6160337</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6040436</t>
+          <t>6089655</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6261619</t>
+          <t>6221444</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>85,74%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3452530</t>
+          <t>3525267</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3659120</t>
+          <t>3730658</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7111650</t>
+          <t>7255925</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
